--- a/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/CAÑUELAS.xlsx
+++ b/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/CAÑUELAS.xlsx
@@ -332,10 +332,6 @@
   </cellStyles>
   <dxfs count="0"/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
